--- a/notebooks/Model_Comparison/results/model_comparison/error_analysis_summary.xlsx
+++ b/notebooks/Model_Comparison/results/model_comparison/error_analysis_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,25 +436,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MAPE (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>R2 Score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean Error</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Median Error</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Max Error</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Top 10 Errors</t>
         </is>
@@ -467,18 +477,24 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>141614.9019710154</v>
+      </c>
+      <c r="C2" t="n">
+        <v>131.3166693038851</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.1533230485853148</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>19781.58634313867</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>2172.368029226232</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>10133570.77990773</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>10,133,571, 3,552,596, 3,229,319, 2,560,442, 2,470,909, 1,597,745, 1,526,178, 1,449,783, 1,412,487, 1,371,568</t>
         </is>
@@ -491,18 +507,24 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>147166.508588011</v>
+      </c>
+      <c r="C3" t="n">
+        <v>124.3983461283009</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.08563877949847076</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>19866.5865045202</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>2437.34765625</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>10130114.2421875</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>10,130,114, 5,367,037, 3,539,316, 2,562,890, 2,468,884, 1,598,467, 1,444,556, 1,328,721, 1,269,245, 1,250,376</t>
         </is>
@@ -515,18 +537,24 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>150822.7482342702</v>
+      </c>
+      <c r="C4" t="n">
+        <v>153.7810182872185</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.03964118864003152</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>20568.20169733818</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>2677.28487942866</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>10125644.90130663</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>10,125,645, 5,977,706, 3,537,683, 2,552,923, 2,462,302, 1,597,842, 1,542,371, 1,447,186, 1,382,346, 1,251,703</t>
         </is>
@@ -539,18 +567,24 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>152039.4693290611</v>
+      </c>
+      <c r="C5" t="n">
+        <v>161.0958018710449</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.02408382651256213</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>21643.49842965811</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>3031.913895542814</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>10140715.79560063</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>10,140,716, 6,010,706, 3,547,939, 2,549,190, 2,476,004, 1,596,513, 1,575,063, 1,447,695, 1,443,233, 1,340,971</t>
         </is>
@@ -563,18 +597,24 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>155254.015657576</v>
+      </c>
+      <c r="C6" t="n">
+        <v>173.8979858588901</v>
+      </c>
+      <c r="D6" t="n">
         <v>-0.01761970827448023</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>23985.88273812434</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>3583.913750575518</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>10141075.37658731</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>10,141,075, 6,011,666, 3,555,244, 2,564,427, 2,469,253, 1,765,281, 1,595,166, 1,447,885, 1,285,781, 1,244,880</t>
         </is>
@@ -587,18 +627,24 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>155259.3739211261</v>
+      </c>
+      <c r="C7" t="n">
+        <v>173.8628126187824</v>
+      </c>
+      <c r="D7" t="n">
         <v>-0.01768995146479524</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>23987.2860304637</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>3588.662968863008</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>10141044.75702388</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>10,141,045, 6,011,640, 3,555,234, 2,564,436, 2,469,233, 1,765,088, 1,595,167, 1,447,885, 1,285,819, 1,244,884</t>
         </is>
@@ -611,18 +657,24 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>155353.4424325848</v>
+      </c>
+      <c r="C8" t="n">
+        <v>204.4470970070549</v>
+      </c>
+      <c r="D8" t="n">
         <v>-0.01892352052614021</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>25793.8137868117</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>5287.700517037335</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>10164122.29948296</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>10,164,122, 6,027,122, 3,566,122, 2,568,122, 2,491,122, 1,842,122, 1,592,122, 1,574,192, 1,461,122, 1,392,122</t>
         </is>
@@ -635,18 +687,24 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>155353.4424325848</v>
+      </c>
+      <c r="C9" t="n">
+        <v>204.4470970070549</v>
+      </c>
+      <c r="D9" t="n">
         <v>-0.01892352052614021</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>25793.8137868117</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>5287.700517037335</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>10164122.29948296</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>10,164,122, 6,027,122, 3,566,122, 2,568,122, 2,491,122, 1,842,122, 1,592,122, 1,574,192, 1,461,122, 1,392,122</t>
         </is>

--- a/notebooks/Model_Comparison/results/model_comparison/error_analysis_summary.xlsx
+++ b/notebooks/Model_Comparison/results/model_comparison/error_analysis_summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MAPE (%)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>R2 Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Mean Error</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Median Error</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Max Error</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Top 10 Errors</t>
         </is>
@@ -477,26 +465,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141614.9019710154</v>
+        <v>7171.14899823854</v>
       </c>
       <c r="C2" t="n">
-        <v>131.3166693038851</v>
+        <v>215.929685071537</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1533230485853148</v>
+        <v>0.4318391807850556</v>
       </c>
       <c r="E2" t="n">
-        <v>19781.58634313867</v>
+        <v>3801.287127201848</v>
       </c>
       <c r="F2" t="n">
-        <v>2172.368029226232</v>
+        <v>1431.998020129192</v>
       </c>
       <c r="G2" t="n">
-        <v>10133570.77990773</v>
+        <v>43185.09200439602</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10,133,571, 3,552,596, 3,229,319, 2,560,442, 2,470,909, 1,597,745, 1,526,178, 1,449,783, 1,412,487, 1,371,568</t>
+          <t>43,185, 40,595, 40,371, 40,338, 39,976, 39,857, 39,775, 39,450, 39,133, 39,119</t>
         </is>
       </c>
     </row>
@@ -507,26 +495,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>147166.508588011</v>
+        <v>7194.426783497633</v>
       </c>
       <c r="C3" t="n">
-        <v>124.3983461283009</v>
+        <v>197.8428741234569</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08563877949847076</v>
+        <v>0.4281446568556855</v>
       </c>
       <c r="E3" t="n">
-        <v>19866.5865045202</v>
+        <v>3780.461145768246</v>
       </c>
       <c r="F3" t="n">
-        <v>2437.34765625</v>
+        <v>1523.616455078125</v>
       </c>
       <c r="G3" t="n">
-        <v>10130114.2421875</v>
+        <v>44283.078125</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10,130,114, 5,367,037, 3,539,316, 2,562,890, 2,468,884, 1,598,467, 1,444,556, 1,328,721, 1,269,245, 1,250,376</t>
+          <t>44,283, 42,756, 40,453, 40,448, 40,059, 39,846, 39,667, 39,529, 39,204, 38,943</t>
         </is>
       </c>
     </row>
@@ -537,26 +525,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150822.7482342702</v>
+        <v>7327.540504000292</v>
       </c>
       <c r="C4" t="n">
-        <v>153.7810182872185</v>
+        <v>221.9688322243714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03964118864003152</v>
+        <v>0.406787567481934</v>
       </c>
       <c r="E4" t="n">
-        <v>20568.20169733818</v>
+        <v>3869.825645206187</v>
       </c>
       <c r="F4" t="n">
-        <v>2677.28487942866</v>
+        <v>1537.308935423115</v>
       </c>
       <c r="G4" t="n">
-        <v>10125644.90130663</v>
+        <v>41705.25317232794</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10,125,645, 5,977,706, 3,537,683, 2,552,923, 2,462,302, 1,597,842, 1,542,371, 1,447,186, 1,382,346, 1,251,703</t>
+          <t>41,705, 40,293, 40,121, 40,092, 39,834, 39,413, 39,275, 39,266, 39,132, 38,751</t>
         </is>
       </c>
     </row>
@@ -567,26 +555,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>152039.4693290611</v>
+        <v>7837.782346228795</v>
       </c>
       <c r="C5" t="n">
-        <v>161.0958018710449</v>
+        <v>239.3206462380737</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02408382651256213</v>
+        <v>0.3212963466117666</v>
       </c>
       <c r="E5" t="n">
-        <v>21643.49842965811</v>
+        <v>4258.925412206682</v>
       </c>
       <c r="F5" t="n">
-        <v>3031.913895542814</v>
+        <v>1742.550123689836</v>
       </c>
       <c r="G5" t="n">
-        <v>10140715.79560063</v>
+        <v>40828.75518691103</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10,140,716, 6,010,706, 3,547,939, 2,549,190, 2,476,004, 1,596,513, 1,575,063, 1,447,695, 1,443,233, 1,340,971</t>
+          <t>40,829, 40,575, 40,010, 39,829, 39,577, 39,522, 39,498, 39,469, 39,352, 39,257</t>
         </is>
       </c>
     </row>
@@ -597,26 +585,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>155254.015657576</v>
+        <v>8845.142338857544</v>
       </c>
       <c r="C6" t="n">
-        <v>173.8979858588901</v>
+        <v>283.9695159345386</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01761970827448023</v>
+        <v>0.1356225247515607</v>
       </c>
       <c r="E6" t="n">
-        <v>23985.88273812434</v>
+        <v>5203.821937565677</v>
       </c>
       <c r="F6" t="n">
-        <v>3583.913750575518</v>
+        <v>2484.951242230627</v>
       </c>
       <c r="G6" t="n">
-        <v>10141075.37658731</v>
+        <v>82590.60730001306</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10,141,075, 6,011,666, 3,555,244, 2,564,427, 2,469,253, 1,765,281, 1,595,166, 1,447,885, 1,285,781, 1,244,880</t>
+          <t>82,591, 44,962, 41,181, 40,573, 40,547, 40,462, 40,421, 40,374, 39,891, 39,833</t>
         </is>
       </c>
     </row>
@@ -627,86 +615,86 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>155259.3739211261</v>
+        <v>8845.236624100355</v>
       </c>
       <c r="C7" t="n">
-        <v>173.8628126187824</v>
+        <v>283.8574147783677</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01768995146479524</v>
+        <v>0.1356040969023801</v>
       </c>
       <c r="E7" t="n">
-        <v>23987.2860304637</v>
+        <v>5203.75088070771</v>
       </c>
       <c r="F7" t="n">
-        <v>3588.662968863008</v>
+        <v>2487.178990324814</v>
       </c>
       <c r="G7" t="n">
-        <v>10141044.75702388</v>
+        <v>82880.59648057004</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10,141,045, 6,011,640, 3,555,234, 2,564,436, 2,469,233, 1,765,088, 1,595,167, 1,447,885, 1,285,819, 1,244,884</t>
+          <t>82,881, 44,978, 41,179, 40,576, 40,545, 40,464, 40,422, 40,382, 39,889, 39,833</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>Dummy Regressor</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>155353.4424325848</v>
+        <v>10128.76749186888</v>
       </c>
       <c r="C8" t="n">
-        <v>204.4470970070549</v>
+        <v>737.8249474934884</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01892352052614021</v>
+        <v>-0.1334620731135752</v>
       </c>
       <c r="E8" t="n">
-        <v>25793.8137868117</v>
+        <v>6276.067049442745</v>
       </c>
       <c r="F8" t="n">
-        <v>5287.700517037335</v>
+        <v>3406.684864881852</v>
       </c>
       <c r="G8" t="n">
-        <v>10164122.29948296</v>
+        <v>39193.31513511814</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10,164,122, 6,027,122, 3,566,122, 2,568,122, 2,491,122, 1,842,122, 1,592,122, 1,574,192, 1,461,122, 1,392,122</t>
+          <t>39,193, 39,193, 39,193, 39,193, 39,193, 39,193, 39,193, 39,193, 39,193, 39,193</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dummy Regressor</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155353.4424325848</v>
+        <v>10128.84372230235</v>
       </c>
       <c r="C9" t="n">
-        <v>204.4470970070549</v>
+        <v>737.8049649302018</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.01892352052614021</v>
+        <v>-0.1334791343464179</v>
       </c>
       <c r="E9" t="n">
-        <v>25793.8137868117</v>
+        <v>6276.117590035783</v>
       </c>
       <c r="F9" t="n">
-        <v>5287.700517037335</v>
+        <v>3406.512836301469</v>
       </c>
       <c r="G9" t="n">
-        <v>10164122.29948296</v>
+        <v>39193.48728988375</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10,164,122, 6,027,122, 3,566,122, 2,568,122, 2,491,122, 1,842,122, 1,592,122, 1,574,192, 1,461,122, 1,392,122</t>
+          <t>39,193, 39,193, 39,193, 39,193, 39,193, 39,193, 39,193, 39,193, 39,193, 39,193</t>
         </is>
       </c>
     </row>
